--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R1cd961ee9db848bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R3c60d3fce1b444be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R4b27f9c81d2c410a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R6de9fa38aa2e46d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R68209218e4b64785"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R26f364fd4fd74973"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Re88c99dbe82e491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R54fd53cd9dff40b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R7b7c5fceed4f400b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rc8ec2932f4b449d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -417,7 +417,7 @@
         <x:v>output/README.txt</x:v>
       </x:c>
       <x:c r="C10" s="6" t="str">
-        <x:v>说明使用者与能力边界</x:v>
+        <x:v>说明使用者与维护窗岗位分工</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>与实际交付互证</x:v>
@@ -880,7 +880,7 @@
         <x:v>措辞和段落可以变化</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>使用者、目录用途、窗口安排和离线能力边界不能写错</x:v>
+        <x:v>使用者、目录用途、窗口安排和现场岗位分工不能写错</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
         <x:v>与结构化交付互证</x:v>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R26f364fd4fd74973"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Re88c99dbe82e491e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R54fd53cd9dff40b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R7b7c5fceed4f400b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rc8ec2932f4b449d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R0106281f97ba4327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R3d337fa5046541b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rb0952f263ba04695"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rbfa254d362884cef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rcd2d188b68744813"/>
   </x:sheets>
 </x:workbook>
 </file>
